--- a/output/yearly_benthic_cover_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_57_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.18872907070079</v>
+        <v>45.32483638294151</v>
       </c>
       <c r="M2" t="n">
-        <v>99.96917897445326</v>
+        <v>99.50300050366891</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95508622998022</v>
+        <v>87.9959269344769</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84124378229383</v>
+        <v>45.91963476840869</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228611573927969</v>
+        <v>2.228656952287781</v>
       </c>
       <c r="E3" t="n">
-        <v>5.652668835481803</v>
+        <v>5.699438847165085</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428705246426562</v>
+        <v>0.7428856507625939</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94348508947822</v>
+        <v>33.97031574692195</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17204413356218</v>
+        <v>34.17273993507932</v>
       </c>
       <c r="I3" t="n">
-        <v>6.572465293870792</v>
+        <v>6.538854484993963</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642940779016601</v>
+        <v>4.643035317266212</v>
       </c>
       <c r="K3" t="n">
-        <v>12.04491377001977</v>
+        <v>12.0040730655231</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87791204614813</v>
+        <v>48.84157306393697</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640695984617</v>
+        <v>106.7652808978688</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09840077252397</v>
+        <v>87.01108876338716</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62379296800088</v>
+        <v>42.56463326007462</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187548880052252</v>
+        <v>2.180823969104115</v>
       </c>
       <c r="E4" t="n">
-        <v>6.463276925015925</v>
+        <v>6.487187537830683</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444309393476686</v>
+        <v>0.7444396617033954</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31806837101095</v>
+        <v>33.24122123993722</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24382320999275</v>
+        <v>34.24422443835618</v>
       </c>
       <c r="I4" t="n">
-        <v>5.488559076181486</v>
+        <v>5.460444030809355</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652693370922928</v>
+        <v>4.65274788564622</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90159922747603</v>
+        <v>12.98891123661283</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29203932413778</v>
+        <v>44.26482065650717</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8174315196147</v>
+        <v>99.81836515319462</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.87603292666796</v>
+        <v>85.80781038675289</v>
       </c>
       <c r="C5" t="n">
-        <v>42.25325714126264</v>
+        <v>42.2087890362202</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127612534139416</v>
+        <v>2.121960069864534</v>
       </c>
       <c r="E5" t="n">
-        <v>7.049846131557002</v>
+        <v>7.071826015355221</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457549149823842</v>
+        <v>0.7457579078377662</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40519127407278</v>
+        <v>32.34398793482451</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30472608918967</v>
+        <v>34.30486376053724</v>
       </c>
       <c r="I5" t="n">
-        <v>4.581933764086794</v>
+        <v>4.558427774347575</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6609682186399</v>
+        <v>4.660986923986038</v>
       </c>
       <c r="K5" t="n">
-        <v>14.12396707333206</v>
+        <v>14.19218961324712</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47031581106692</v>
+        <v>43.44734234967687</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84754002566162</v>
+        <v>99.84832099914418</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.36772091971275</v>
+        <v>84.27009487737462</v>
       </c>
       <c r="C6" t="n">
-        <v>41.45647253725288</v>
+        <v>41.37893138716316</v>
       </c>
       <c r="D6" t="n">
-        <v>2.053536371039483</v>
+        <v>2.04648077794207</v>
       </c>
       <c r="E6" t="n">
-        <v>7.44173586874395</v>
+        <v>7.454344966678226</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468816499641607</v>
+        <v>0.7468801588784675</v>
       </c>
       <c r="G6" t="n">
-        <v>31.27695377989309</v>
+        <v>31.19349441614811</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35655589835139</v>
+        <v>34.35648730840951</v>
       </c>
       <c r="I6" t="n">
-        <v>3.824047039444675</v>
+        <v>3.804406256327823</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668010312276003</v>
+        <v>4.668000992990422</v>
       </c>
       <c r="K6" t="n">
-        <v>15.63227908028726</v>
+        <v>15.72990512262538</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78397244456857</v>
+        <v>42.7645404964796</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8727240621087</v>
+        <v>99.87337700626813</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.74504122058039</v>
+        <v>82.49971214068978</v>
       </c>
       <c r="C7" t="n">
-        <v>40.42754561487563</v>
+        <v>40.19920734078535</v>
       </c>
       <c r="D7" t="n">
-        <v>1.974342941171973</v>
+        <v>1.959960431649209</v>
       </c>
       <c r="E7" t="n">
-        <v>7.686550014991953</v>
+        <v>7.668260434209865</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478416879550962</v>
+        <v>0.7478381015988516</v>
       </c>
       <c r="G7" t="n">
-        <v>30.07077633859289</v>
+        <v>29.87470756602997</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40071764593442</v>
+        <v>34.40055267354717</v>
       </c>
       <c r="I7" t="n">
-        <v>3.190802042214699</v>
+        <v>3.174404798661889</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674010549719349</v>
+        <v>4.673988134992822</v>
       </c>
       <c r="K7" t="n">
-        <v>17.25495877941963</v>
+        <v>17.50028785931022</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21127207683129</v>
+        <v>42.19482684833978</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89377647112654</v>
+        <v>99.89432204843536</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.48308623779548</v>
+        <v>87.37915183738561</v>
       </c>
       <c r="C8" t="n">
-        <v>42.6953744069224</v>
+        <v>42.45533661870348</v>
       </c>
       <c r="D8" t="n">
-        <v>1.978510825153082</v>
+        <v>1.964201923231258</v>
       </c>
       <c r="E8" t="n">
-        <v>9.490935334892081</v>
+        <v>9.472906708742784</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494203991944836</v>
+        <v>0.7494564756034725</v>
       </c>
       <c r="G8" t="n">
-        <v>30.566638778509</v>
+        <v>30.36064783167482</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47333836294624</v>
+        <v>34.47499787775974</v>
       </c>
       <c r="I8" t="n">
-        <v>5.540365042135075</v>
+        <v>5.672838047851828</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683877494965521</v>
+        <v>4.684102972521702</v>
       </c>
       <c r="K8" t="n">
-        <v>12.5169137622045</v>
+        <v>12.62084816261441</v>
       </c>
       <c r="L8" t="n">
-        <v>44.60342203618861</v>
+        <v>44.7351289473872</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81571020531553</v>
+        <v>99.81131372870507</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.30715955824478</v>
+        <v>85.31998886697222</v>
       </c>
       <c r="C9" t="n">
-        <v>41.37907380293893</v>
+        <v>41.27594414215172</v>
       </c>
       <c r="D9" t="n">
-        <v>1.879487269432967</v>
+        <v>1.87089105827924</v>
       </c>
       <c r="E9" t="n">
-        <v>9.786804259077636</v>
+        <v>9.812241310092</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507748402457491</v>
+        <v>0.7508432198021288</v>
       </c>
       <c r="G9" t="n">
-        <v>29.03679258318878</v>
+        <v>28.91834280377998</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53564265130446</v>
+        <v>34.53878811089793</v>
       </c>
       <c r="I9" t="n">
-        <v>4.625315203459249</v>
+        <v>4.736112240357645</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69234275153593</v>
+        <v>4.692770123763304</v>
       </c>
       <c r="K9" t="n">
-        <v>14.6928404417552</v>
+        <v>14.68001113302778</v>
       </c>
       <c r="L9" t="n">
-        <v>43.77418672635766</v>
+        <v>43.88646589015796</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84610097105181</v>
+        <v>99.84242116533746</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.9359405102654</v>
+        <v>83.14977647126149</v>
       </c>
       <c r="C10" t="n">
-        <v>39.72504479333509</v>
+        <v>39.83989936295896</v>
       </c>
       <c r="D10" t="n">
-        <v>1.772741185616718</v>
+        <v>1.77369532445285</v>
       </c>
       <c r="E10" t="n">
-        <v>9.874361185168157</v>
+        <v>9.961315706600477</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519397145962315</v>
+        <v>0.7520330783718032</v>
       </c>
       <c r="G10" t="n">
-        <v>27.38763861165098</v>
+        <v>27.41598939981337</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58922687142665</v>
+        <v>34.59352160510295</v>
       </c>
       <c r="I10" t="n">
-        <v>3.860409725580228</v>
+        <v>3.953014617096277</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699623216226446</v>
+        <v>4.70020673982377</v>
       </c>
       <c r="K10" t="n">
-        <v>17.06405948973459</v>
+        <v>16.8502235287385</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08241473905643</v>
+        <v>43.17831843495927</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87151902212611</v>
+        <v>99.86844132665672</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.42843320605679</v>
+        <v>80.90302226156535</v>
       </c>
       <c r="C11" t="n">
-        <v>37.81534141026516</v>
+        <v>38.20530910747242</v>
       </c>
       <c r="D11" t="n">
-        <v>1.661078810183703</v>
+        <v>1.674180752252812</v>
       </c>
       <c r="E11" t="n">
-        <v>9.789273444794992</v>
+        <v>9.952204242304584</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752943599070083</v>
+        <v>0.7530551656100249</v>
       </c>
       <c r="G11" t="n">
-        <v>25.66253129779681</v>
+        <v>25.87779373624594</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63540555722382</v>
+        <v>34.64053761806115</v>
       </c>
       <c r="I11" t="n">
-        <v>3.221303002799368</v>
+        <v>3.298655962028203</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705897494188018</v>
+        <v>4.706594785062656</v>
       </c>
       <c r="K11" t="n">
-        <v>19.57156679394321</v>
+        <v>19.09697773843462</v>
       </c>
       <c r="L11" t="n">
-        <v>42.50585819230328</v>
+        <v>42.58790719250695</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89276639651166</v>
+        <v>99.89019403841399</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.77268442399294</v>
+        <v>78.56189311483679</v>
       </c>
       <c r="C12" t="n">
-        <v>35.65748156461498</v>
+        <v>36.37425141107756</v>
       </c>
       <c r="D12" t="n">
-        <v>1.543990635096642</v>
+        <v>1.571506007733795</v>
       </c>
       <c r="E12" t="n">
-        <v>9.547153588970785</v>
+        <v>9.800533605992763</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538108891800156</v>
+        <v>0.7539345043387057</v>
       </c>
       <c r="G12" t="n">
-        <v>23.85359909099724</v>
+        <v>24.29075132340636</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67530090228072</v>
+        <v>34.68098719958046</v>
       </c>
       <c r="I12" t="n">
-        <v>2.687511260092434</v>
+        <v>2.752089821667798</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711318057375097</v>
+        <v>4.71209065211691</v>
       </c>
       <c r="K12" t="n">
-        <v>22.22731557600706</v>
+        <v>21.43810688516322</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02572222041131</v>
+        <v>42.09601237148064</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91051936103335</v>
+        <v>99.90837066772141</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.13861071749966</v>
+        <v>76.33526005146707</v>
       </c>
       <c r="C13" t="n">
-        <v>33.43774595054202</v>
+        <v>34.5723270755558</v>
       </c>
       <c r="D13" t="n">
-        <v>1.42902711142772</v>
+        <v>1.474864875714113</v>
       </c>
       <c r="E13" t="n">
-        <v>9.209921692353973</v>
+        <v>9.580459122671503</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545605740401364</v>
+        <v>0.7546902987588016</v>
       </c>
       <c r="G13" t="n">
-        <v>22.07749129516517</v>
+        <v>22.7969703935531</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70978640584628</v>
+        <v>34.71575374290487</v>
       </c>
       <c r="I13" t="n">
-        <v>2.241820050915541</v>
+        <v>2.295707250622181</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716003587750852</v>
+        <v>4.716814367242509</v>
       </c>
       <c r="K13" t="n">
-        <v>24.86138928250034</v>
+        <v>23.66473994853291</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62621167639951</v>
+        <v>41.68648603642053</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92534690944186</v>
+        <v>99.92355306050925</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.5670765632583</v>
+        <v>83.34893061744339</v>
       </c>
       <c r="C14" t="n">
-        <v>38.07896975362311</v>
+        <v>38.74037758483995</v>
       </c>
       <c r="D14" t="n">
-        <v>1.430704156180359</v>
+        <v>1.476797899468451</v>
       </c>
       <c r="E14" t="n">
-        <v>11.76966138198667</v>
+        <v>11.93552292620044</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755446093874661</v>
+        <v>0.755679429558979</v>
       </c>
       <c r="G14" t="n">
-        <v>24.16784596263115</v>
+        <v>24.62315219811469</v>
       </c>
       <c r="H14" t="n">
-        <v>36.81496579151371</v>
+        <v>36.5575568370615</v>
       </c>
       <c r="I14" t="n">
-        <v>2.906915090355108</v>
+        <v>3.277224892295703</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721538086716631</v>
+        <v>4.722996434743618</v>
       </c>
       <c r="K14" t="n">
-        <v>17.43292343674174</v>
+        <v>16.65106938255662</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39132322101342</v>
+        <v>44.49945519136183</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90321641137825</v>
+        <v>99.89090215875841</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.65910719898559</v>
+        <v>82.8015670024176</v>
       </c>
       <c r="C15" t="n">
-        <v>37.61942643739393</v>
+        <v>38.69895896224675</v>
       </c>
       <c r="D15" t="n">
-        <v>1.397322764325385</v>
+        <v>1.457147513121569</v>
       </c>
       <c r="E15" t="n">
-        <v>11.89918781080597</v>
+        <v>12.23237904050633</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561938472079602</v>
+        <v>0.7565111560325509</v>
       </c>
       <c r="G15" t="n">
-        <v>23.60395836023325</v>
+        <v>24.29551464260005</v>
       </c>
       <c r="H15" t="n">
-        <v>36.85140586792566</v>
+        <v>36.59779332708775</v>
       </c>
       <c r="I15" t="n">
-        <v>2.424827003437627</v>
+        <v>2.734026597865921</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726211545049751</v>
+        <v>4.728194725203442</v>
       </c>
       <c r="K15" t="n">
-        <v>18.34089280101441</v>
+        <v>17.19843299758239</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95893312019292</v>
+        <v>44.01157401538488</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91925235860126</v>
+        <v>99.90896597521402</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.07023850288677</v>
+        <v>80.54232009801966</v>
       </c>
       <c r="C16" t="n">
-        <v>35.40457561472896</v>
+        <v>36.86203136423279</v>
       </c>
       <c r="D16" t="n">
-        <v>1.300396930336965</v>
+        <v>1.371773820201542</v>
       </c>
       <c r="E16" t="n">
-        <v>11.41086470764505</v>
+        <v>11.89577312691148</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568385632295456</v>
+        <v>0.7572251608383426</v>
       </c>
       <c r="G16" t="n">
-        <v>21.96666065929865</v>
+        <v>22.87205010812205</v>
       </c>
       <c r="H16" t="n">
-        <v>36.88282465276333</v>
+        <v>36.63233478772391</v>
       </c>
       <c r="I16" t="n">
-        <v>2.022411969428566</v>
+        <v>2.280505838982685</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73024102018466</v>
+        <v>4.732657255239641</v>
       </c>
       <c r="K16" t="n">
-        <v>20.92976149711324</v>
+        <v>19.45767990198036</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59830658250677</v>
+        <v>43.60434355051279</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93264369434897</v>
+        <v>99.92405481672594</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.79571899796279</v>
+        <v>82.4550395152496</v>
       </c>
       <c r="C17" t="n">
-        <v>36.66167768043213</v>
+        <v>38.21799039581547</v>
       </c>
       <c r="D17" t="n">
-        <v>1.30147506028703</v>
+        <v>1.373065964383902</v>
       </c>
       <c r="E17" t="n">
-        <v>12.20175701391973</v>
+        <v>12.76235628077371</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574660411198312</v>
+        <v>0.7579384300900988</v>
       </c>
       <c r="G17" t="n">
-        <v>22.4313749403981</v>
+        <v>23.36062920767285</v>
       </c>
       <c r="H17" t="n">
-        <v>37.35990559112432</v>
+        <v>37.13387540580971</v>
       </c>
       <c r="I17" t="n">
-        <v>2.009577594114837</v>
+        <v>2.330059038456209</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734162756998945</v>
+        <v>4.737115188063117</v>
       </c>
       <c r="K17" t="n">
-        <v>19.20428100203722</v>
+        <v>17.54496048475039</v>
       </c>
       <c r="L17" t="n">
-        <v>44.06711088824568</v>
+        <v>44.1594535760447</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93306957071502</v>
+        <v>99.92240445661056</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.33908190014895</v>
+        <v>80.27277144834164</v>
       </c>
       <c r="C18" t="n">
-        <v>34.51454395709348</v>
+        <v>36.39534112690928</v>
       </c>
       <c r="D18" t="n">
-        <v>1.213365488432167</v>
+        <v>1.294197113117225</v>
       </c>
       <c r="E18" t="n">
-        <v>11.655007803637</v>
+        <v>12.35316752798281</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580061689335544</v>
+        <v>0.7585500483000658</v>
       </c>
       <c r="G18" t="n">
-        <v>20.91277585047126</v>
+        <v>22.01879564813033</v>
       </c>
       <c r="H18" t="n">
-        <v>37.38654589317405</v>
+        <v>37.16384057646631</v>
       </c>
       <c r="I18" t="n">
-        <v>1.675842139666205</v>
+        <v>1.943282732469506</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737538555834715</v>
+        <v>4.740937801875411</v>
       </c>
       <c r="K18" t="n">
-        <v>21.66091809985105</v>
+        <v>19.72722855165836</v>
       </c>
       <c r="L18" t="n">
-        <v>43.76871634321897</v>
+        <v>43.812706459253</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94417840016351</v>
+        <v>99.93527613782064</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.34894025303083</v>
+        <v>79.48938586773788</v>
       </c>
       <c r="C19" t="n">
-        <v>33.77631672671328</v>
+        <v>35.91122513643634</v>
       </c>
       <c r="D19" t="n">
-        <v>1.178285531096548</v>
+        <v>1.266631008945976</v>
       </c>
       <c r="E19" t="n">
-        <v>11.55182309439046</v>
+        <v>12.36013165855632</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584643628660422</v>
+        <v>0.7590655185588813</v>
       </c>
       <c r="G19" t="n">
-        <v>20.3081605951356</v>
+        <v>21.5498003085411</v>
       </c>
       <c r="H19" t="n">
-        <v>37.40914503443042</v>
+        <v>37.18909514544756</v>
       </c>
       <c r="I19" t="n">
-        <v>1.402659367198988</v>
+        <v>1.620502736695031</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740402267912764</v>
+        <v>4.744159490993008</v>
       </c>
       <c r="K19" t="n">
-        <v>22.65105974696917</v>
+        <v>20.51061413226211</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5258964593076</v>
+        <v>43.52418065539964</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95327293299005</v>
+        <v>99.9460199240981</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.69609105904624</v>
+        <v>77.09936035165721</v>
       </c>
       <c r="C20" t="n">
-        <v>31.33869819050391</v>
+        <v>33.77067280306257</v>
       </c>
       <c r="D20" t="n">
-        <v>1.084239176777845</v>
+        <v>1.181261095075911</v>
       </c>
       <c r="E20" t="n">
-        <v>10.82471515288148</v>
+        <v>11.75227000734556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588601973397751</v>
+        <v>0.7595089529687189</v>
       </c>
       <c r="G20" t="n">
-        <v>18.68723899634976</v>
+        <v>20.09736105570128</v>
       </c>
       <c r="H20" t="n">
-        <v>37.42866846883616</v>
+        <v>37.21082044327103</v>
       </c>
       <c r="I20" t="n">
-        <v>1.16949283348762</v>
+        <v>1.351207841240204</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742876233373594</v>
+        <v>4.746930956054493</v>
       </c>
       <c r="K20" t="n">
-        <v>25.30390894095378</v>
+        <v>22.9006396483428</v>
       </c>
       <c r="L20" t="n">
-        <v>43.31843010834234</v>
+        <v>43.28367358368642</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96103723980002</v>
+        <v>99.95498603509179</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.83166078141525</v>
+        <v>82.79690370082244</v>
       </c>
       <c r="C21" t="n">
-        <v>35.17439347085824</v>
+        <v>37.19146136605147</v>
       </c>
       <c r="D21" t="n">
-        <v>1.084981454917062</v>
+        <v>1.182236640010936</v>
       </c>
       <c r="E21" t="n">
-        <v>12.88144805887242</v>
+        <v>13.63485477290051</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593797186292387</v>
+        <v>0.7601361937330706</v>
       </c>
       <c r="G21" t="n">
-        <v>20.47266488770291</v>
+        <v>21.64494834224816</v>
       </c>
       <c r="H21" t="n">
-        <v>39.22692488106794</v>
+        <v>38.77254088691238</v>
       </c>
       <c r="I21" t="n">
-        <v>1.660138538792935</v>
+        <v>2.051335654185677</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746123241432742</v>
+        <v>4.750851210831692</v>
       </c>
       <c r="K21" t="n">
-        <v>19.16833921858474</v>
+        <v>17.20309629917756</v>
       </c>
       <c r="L21" t="n">
-        <v>45.60196721811517</v>
+        <v>45.53712090291253</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94469990755815</v>
+        <v>99.93167856814156</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_57_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32483638294151</v>
+        <v>45.44395466523776</v>
       </c>
       <c r="M2" t="n">
-        <v>99.50300050366891</v>
+        <v>99.05742527850543</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9959269344769</v>
+        <v>88.05563682984919</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91963476840869</v>
+        <v>45.9367283594781</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228656952287781</v>
+        <v>2.228797162345612</v>
       </c>
       <c r="E3" t="n">
-        <v>5.699438847165085</v>
+        <v>5.712507988546333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428856507625939</v>
+        <v>0.7429323874485374</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97031574692195</v>
+        <v>33.97561655126201</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17273993507932</v>
+        <v>34.17488982263271</v>
       </c>
       <c r="I3" t="n">
-        <v>6.538854484993963</v>
+        <v>6.577565496060616</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643035317266212</v>
+        <v>4.643327421553359</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0040730655231</v>
+        <v>11.94436317015081</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84157306393697</v>
+        <v>48.8828146487462</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652808978688</v>
+        <v>106.7639061783751</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.01108876338716</v>
+        <v>87.09691673479496</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56463326007462</v>
+        <v>42.61468475789</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180823969104115</v>
+        <v>2.182398503910339</v>
       </c>
       <c r="E4" t="n">
-        <v>6.487187537830683</v>
+        <v>6.509057347639309</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444396617033954</v>
+        <v>0.7444941722852284</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24122123993722</v>
+        <v>33.26831888679857</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24422443835618</v>
+        <v>34.2467319251205</v>
       </c>
       <c r="I4" t="n">
-        <v>5.460444030809355</v>
+        <v>5.492827322258331</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65274788564622</v>
+        <v>4.653088576782677</v>
       </c>
       <c r="K4" t="n">
-        <v>12.98891123661283</v>
+        <v>12.90308326520506</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26482065650717</v>
+        <v>44.29952182423659</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81836515319462</v>
+        <v>99.81728984733164</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.80781038675289</v>
+        <v>85.9559032470048</v>
       </c>
       <c r="C5" t="n">
-        <v>42.2087890362202</v>
+        <v>42.32614810649031</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121960069864534</v>
+        <v>2.126827759781893</v>
       </c>
       <c r="E5" t="n">
-        <v>7.071826015355221</v>
+        <v>7.107565519777093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457579078377662</v>
+        <v>0.7458180584142844</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34398793482451</v>
+        <v>32.42120263688852</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30486376053724</v>
+        <v>34.30763068705708</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558427774347575</v>
+        <v>4.585495719996656</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660986923986038</v>
+        <v>4.661362865089277</v>
       </c>
       <c r="K5" t="n">
-        <v>14.19218961324712</v>
+        <v>14.04409675299519</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44734234967687</v>
+        <v>43.47717660378513</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84832099914418</v>
+        <v>99.84742146327062</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.27009487737462</v>
+        <v>84.57569745851038</v>
       </c>
       <c r="C6" t="n">
-        <v>41.37893138716316</v>
+        <v>41.65808259192244</v>
       </c>
       <c r="D6" t="n">
-        <v>2.04648077794207</v>
+        <v>2.059459637173455</v>
       </c>
       <c r="E6" t="n">
-        <v>7.454344966678226</v>
+        <v>7.520265544622715</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468801588784675</v>
+        <v>0.7469429888287863</v>
       </c>
       <c r="G6" t="n">
-        <v>31.19349441614811</v>
+        <v>31.39424803545952</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35648730840951</v>
+        <v>34.35937748612417</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804406256327823</v>
+        <v>3.827010086121819</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668000992990422</v>
+        <v>4.668393680179914</v>
       </c>
       <c r="K6" t="n">
-        <v>15.72990512262538</v>
+        <v>15.42430254148963</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7645404964796</v>
+        <v>42.7902399854769</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87337700626813</v>
+        <v>99.87262511888896</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.49971214068978</v>
+        <v>83.02398743488614</v>
       </c>
       <c r="C7" t="n">
-        <v>40.19920734078535</v>
+        <v>40.70073536108826</v>
       </c>
       <c r="D7" t="n">
-        <v>1.959960431649209</v>
+        <v>1.984006979552205</v>
       </c>
       <c r="E7" t="n">
-        <v>7.668260434209865</v>
+        <v>7.77695535157662</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478381015988516</v>
+        <v>0.7479006180959755</v>
       </c>
       <c r="G7" t="n">
-        <v>29.87470756602997</v>
+        <v>30.24405338947597</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40055267354717</v>
+        <v>34.40342843241487</v>
       </c>
       <c r="I7" t="n">
-        <v>3.174404798661889</v>
+        <v>3.193263800670644</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673988134992822</v>
+        <v>4.674378863099847</v>
       </c>
       <c r="K7" t="n">
-        <v>17.50028785931022</v>
+        <v>16.97601256511388</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19482684833978</v>
+        <v>42.21694623807227</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89432204843536</v>
+        <v>99.89369416427439</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.37915183738561</v>
+        <v>87.93808690409263</v>
       </c>
       <c r="C8" t="n">
-        <v>42.45533661870348</v>
+        <v>43.00963300447293</v>
       </c>
       <c r="D8" t="n">
-        <v>1.964201923231258</v>
+        <v>1.988274164126698</v>
       </c>
       <c r="E8" t="n">
-        <v>9.472906708742784</v>
+        <v>9.616622978580279</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494564756034725</v>
+        <v>0.7495091960968018</v>
       </c>
       <c r="G8" t="n">
-        <v>30.36064783167482</v>
+        <v>30.7477314019946</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47499787775974</v>
+        <v>34.47742302045287</v>
       </c>
       <c r="I8" t="n">
-        <v>5.672838047851828</v>
+        <v>5.674093667236359</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684102972521702</v>
+        <v>4.684432475605011</v>
       </c>
       <c r="K8" t="n">
-        <v>12.62084816261441</v>
+        <v>12.06191309590737</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7351289473872</v>
+        <v>44.73972336400342</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81131372870507</v>
+        <v>99.81126946438373</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.31998886697222</v>
+        <v>85.89995442376498</v>
       </c>
       <c r="C9" t="n">
-        <v>41.27594414215172</v>
+        <v>41.85207382536466</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87089105827924</v>
+        <v>1.896071601313419</v>
       </c>
       <c r="E9" t="n">
-        <v>9.812241310092</v>
+        <v>9.960186961496126</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508432198021288</v>
+        <v>0.7508869626276579</v>
       </c>
       <c r="G9" t="n">
-        <v>28.91834280377998</v>
+        <v>29.3218618277131</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53878811089793</v>
+        <v>34.54080028087225</v>
       </c>
       <c r="I9" t="n">
-        <v>4.736112240357645</v>
+        <v>4.737103273319573</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692770123763304</v>
+        <v>4.693043516422861</v>
       </c>
       <c r="K9" t="n">
-        <v>14.68001113302778</v>
+        <v>14.10004557623502</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88646589015796</v>
+        <v>43.89026688542151</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84242116533746</v>
+        <v>99.8423862870212</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.14977647126149</v>
+        <v>83.73496801572254</v>
       </c>
       <c r="C10" t="n">
-        <v>39.83989936295896</v>
+        <v>40.42195195529117</v>
       </c>
       <c r="D10" t="n">
-        <v>1.77369532445285</v>
+        <v>1.799210874209183</v>
       </c>
       <c r="E10" t="n">
-        <v>9.961315706600477</v>
+        <v>10.11033783689777</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520330783718032</v>
+        <v>0.7520688091203176</v>
       </c>
       <c r="G10" t="n">
-        <v>27.41598939981337</v>
+        <v>27.82395591808665</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59352160510295</v>
+        <v>34.5951652195346</v>
       </c>
       <c r="I10" t="n">
-        <v>3.953014617096277</v>
+        <v>3.953799300872056</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70020673982377</v>
+        <v>4.700430057001984</v>
       </c>
       <c r="K10" t="n">
-        <v>16.8502235287385</v>
+        <v>16.26503198427742</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17831843495927</v>
+        <v>43.18142985839476</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86844132665672</v>
+        <v>99.86841379796336</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.90302226156535</v>
+        <v>81.43544948115459</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20530910747242</v>
+        <v>38.73519369553374</v>
       </c>
       <c r="D11" t="n">
-        <v>1.674180752252812</v>
+        <v>1.697373332491654</v>
       </c>
       <c r="E11" t="n">
-        <v>9.952204242304584</v>
+        <v>10.08796070466795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530551656100249</v>
+        <v>0.7530844549855022</v>
       </c>
       <c r="G11" t="n">
-        <v>25.87779373624594</v>
+        <v>26.24908589469361</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64053761806115</v>
+        <v>34.6418849293331</v>
       </c>
       <c r="I11" t="n">
-        <v>3.298655962028203</v>
+        <v>3.299282321323405</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706594785062656</v>
+        <v>4.706777843659388</v>
       </c>
       <c r="K11" t="n">
-        <v>19.09697773843462</v>
+        <v>18.56455051884539</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58790719250695</v>
+        <v>42.5904280272633</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89019403841399</v>
+        <v>99.89017224164243</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.56189311483679</v>
+        <v>79.06569013593801</v>
       </c>
       <c r="C12" t="n">
-        <v>36.37425141107756</v>
+        <v>36.8759786973615</v>
       </c>
       <c r="D12" t="n">
-        <v>1.571506007733795</v>
+        <v>1.593464398384799</v>
       </c>
       <c r="E12" t="n">
-        <v>9.800533605992763</v>
+        <v>9.929166497008318</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539345043387057</v>
+        <v>0.7539583842615295</v>
       </c>
       <c r="G12" t="n">
-        <v>24.29075132340636</v>
+        <v>24.642182755363</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68098719958046</v>
+        <v>34.68208567603035</v>
       </c>
       <c r="I12" t="n">
-        <v>2.752089821667798</v>
+        <v>2.752592523255477</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71209065211691</v>
+        <v>4.712239901634559</v>
       </c>
       <c r="K12" t="n">
-        <v>21.43810688516322</v>
+        <v>20.93430986406197</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09601237148064</v>
+        <v>42.09806470742866</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90837066772141</v>
+        <v>99.90835326885214</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.33526005146707</v>
+        <v>76.72757760647109</v>
       </c>
       <c r="C13" t="n">
-        <v>34.5723270755558</v>
+        <v>34.96296402266951</v>
       </c>
       <c r="D13" t="n">
-        <v>1.474864875714113</v>
+        <v>1.491931144928959</v>
       </c>
       <c r="E13" t="n">
-        <v>9.580459122671503</v>
+        <v>9.679180200062151</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546902987588016</v>
+        <v>0.7547104716633075</v>
       </c>
       <c r="G13" t="n">
-        <v>22.7969703935531</v>
+        <v>23.07201840783095</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71575374290487</v>
+        <v>34.71668169651213</v>
       </c>
       <c r="I13" t="n">
-        <v>2.295707250622181</v>
+        <v>2.296115237577923</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716814367242509</v>
+        <v>4.716940447895672</v>
       </c>
       <c r="K13" t="n">
-        <v>23.66473994853291</v>
+        <v>23.27242239352892</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68648603642053</v>
+        <v>41.6881526803778</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92355306050925</v>
+        <v>99.92353909657622</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.34893061744339</v>
+        <v>83.58616995017464</v>
       </c>
       <c r="C14" t="n">
-        <v>38.74037758483995</v>
+        <v>39.09047789222888</v>
       </c>
       <c r="D14" t="n">
-        <v>1.476797899468451</v>
+        <v>1.49382224769342</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93552292620044</v>
+        <v>12.00523661948882</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755679429558979</v>
+        <v>0.7556671076744141</v>
       </c>
       <c r="G14" t="n">
-        <v>24.62315219811469</v>
+        <v>24.8853011952041</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5575568370615</v>
+        <v>36.54472471930988</v>
       </c>
       <c r="I14" t="n">
-        <v>3.277224892295703</v>
+        <v>3.178498637838909</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722996434743618</v>
+        <v>4.722919422965088</v>
       </c>
       <c r="K14" t="n">
-        <v>16.65106938255662</v>
+        <v>16.41383004982538</v>
       </c>
       <c r="L14" t="n">
-        <v>44.49945519136183</v>
+        <v>44.38987623058905</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89090215875841</v>
+        <v>99.89418417264331</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.8015670024176</v>
+        <v>82.86649979557649</v>
       </c>
       <c r="C15" t="n">
-        <v>38.69895896224675</v>
+        <v>38.86181515960693</v>
       </c>
       <c r="D15" t="n">
-        <v>1.457147513121569</v>
+        <v>1.467377949487424</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23237904050633</v>
+        <v>12.23464364809204</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565111560325509</v>
+        <v>0.7564731057899393</v>
       </c>
       <c r="G15" t="n">
-        <v>24.29551464260005</v>
+        <v>24.44477065231781</v>
       </c>
       <c r="H15" t="n">
-        <v>36.59779332708775</v>
+        <v>36.58370349575391</v>
       </c>
       <c r="I15" t="n">
-        <v>2.734026597865921</v>
+        <v>2.651574032948237</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728194725203442</v>
+        <v>4.72795691118712</v>
       </c>
       <c r="K15" t="n">
-        <v>17.19843299758239</v>
+        <v>17.13350020442351</v>
       </c>
       <c r="L15" t="n">
-        <v>44.01157401538488</v>
+        <v>43.91639300714073</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90896597521402</v>
+        <v>99.91170837117116</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.54232009801966</v>
+        <v>80.54020934045552</v>
       </c>
       <c r="C16" t="n">
-        <v>36.86203136423279</v>
+        <v>36.94524907180904</v>
       </c>
       <c r="D16" t="n">
-        <v>1.371773820201542</v>
+        <v>1.37915468235703</v>
       </c>
       <c r="E16" t="n">
-        <v>11.89577312691148</v>
+        <v>11.86767058194127</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7572251608383426</v>
+        <v>0.7571655413187424</v>
       </c>
       <c r="G16" t="n">
-        <v>22.87205010812205</v>
+        <v>22.97507599597247</v>
       </c>
       <c r="H16" t="n">
-        <v>36.63233478772391</v>
+        <v>36.61719028580866</v>
       </c>
       <c r="I16" t="n">
-        <v>2.280505838982685</v>
+        <v>2.211667619815196</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732657255239641</v>
+        <v>4.732284633242139</v>
       </c>
       <c r="K16" t="n">
-        <v>19.45767990198036</v>
+        <v>19.45979065954449</v>
       </c>
       <c r="L16" t="n">
-        <v>43.60434355051279</v>
+        <v>43.5213054343979</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92405481672594</v>
+        <v>99.92634516575143</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.4550395152496</v>
+        <v>82.27313148312975</v>
       </c>
       <c r="C17" t="n">
-        <v>38.21799039581547</v>
+        <v>38.19141587945891</v>
       </c>
       <c r="D17" t="n">
-        <v>1.373065964383902</v>
+        <v>1.380406326367006</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76235628077371</v>
+        <v>12.67183197291431</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7579384300900988</v>
+        <v>0.7578527026114349</v>
       </c>
       <c r="G17" t="n">
-        <v>23.36062920767285</v>
+        <v>23.41598528044157</v>
       </c>
       <c r="H17" t="n">
-        <v>37.13387540580971</v>
+        <v>37.07048039372905</v>
       </c>
       <c r="I17" t="n">
-        <v>2.330059038456209</v>
+        <v>2.239995415744902</v>
       </c>
       <c r="J17" t="n">
-        <v>4.737115188063117</v>
+        <v>4.736579391321468</v>
       </c>
       <c r="K17" t="n">
-        <v>17.54496048475039</v>
+        <v>17.72686851687028</v>
       </c>
       <c r="L17" t="n">
-        <v>44.1594535760447</v>
+        <v>44.00711679154151</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92240445661056</v>
+        <v>99.92540118787068</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.27277144834164</v>
+        <v>80.03743670615663</v>
       </c>
       <c r="C18" t="n">
-        <v>36.39534112690928</v>
+        <v>36.30149197977025</v>
       </c>
       <c r="D18" t="n">
-        <v>1.294197113117225</v>
+        <v>1.299048634574488</v>
       </c>
       <c r="E18" t="n">
-        <v>12.35316752798281</v>
+        <v>12.2363384554295</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585500483000658</v>
+        <v>0.758442325071312</v>
       </c>
       <c r="G18" t="n">
-        <v>22.01879564813033</v>
+        <v>22.03590575090325</v>
       </c>
       <c r="H18" t="n">
-        <v>37.16384057646631</v>
+        <v>37.09932186617252</v>
       </c>
       <c r="I18" t="n">
-        <v>1.943282732469506</v>
+        <v>1.868115142309856</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740937801875411</v>
+        <v>4.7402645316957</v>
       </c>
       <c r="K18" t="n">
-        <v>19.72722855165836</v>
+        <v>19.96256329384337</v>
       </c>
       <c r="L18" t="n">
-        <v>43.812706459253</v>
+        <v>43.6737226315046</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93527613782064</v>
+        <v>99.93777790511822</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.48938586773788</v>
+        <v>79.20691741827198</v>
       </c>
       <c r="C19" t="n">
-        <v>35.91122513643634</v>
+        <v>35.75867631452584</v>
       </c>
       <c r="D19" t="n">
-        <v>1.266631008945976</v>
+        <v>1.269550160517641</v>
       </c>
       <c r="E19" t="n">
-        <v>12.36013165855632</v>
+        <v>12.21810925033617</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7590655185588813</v>
+        <v>0.7589395412009224</v>
       </c>
       <c r="G19" t="n">
-        <v>21.5498003085411</v>
+        <v>21.53551987095114</v>
       </c>
       <c r="H19" t="n">
-        <v>37.18909514544756</v>
+        <v>37.12364326889452</v>
       </c>
       <c r="I19" t="n">
-        <v>1.620502736695031</v>
+        <v>1.557783193865831</v>
       </c>
       <c r="J19" t="n">
-        <v>4.744159490993008</v>
+        <v>4.743372132505765</v>
       </c>
       <c r="K19" t="n">
-        <v>20.51061413226211</v>
+        <v>20.793082581728</v>
       </c>
       <c r="L19" t="n">
-        <v>43.52418065539964</v>
+        <v>43.39634901645977</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9460199240981</v>
+        <v>99.94810791271361</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.09936035165721</v>
+        <v>76.78816596436505</v>
       </c>
       <c r="C20" t="n">
-        <v>33.77067280306257</v>
+        <v>33.57972614602473</v>
       </c>
       <c r="D20" t="n">
-        <v>1.181261095075911</v>
+        <v>1.182539574937768</v>
       </c>
       <c r="E20" t="n">
-        <v>11.75227000734556</v>
+        <v>11.59720298702108</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7595089529687189</v>
+        <v>0.7593674608236867</v>
       </c>
       <c r="G20" t="n">
-        <v>20.09736105570128</v>
+        <v>20.05954967850563</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21082044327103</v>
+        <v>37.14457502242804</v>
       </c>
       <c r="I20" t="n">
-        <v>1.351207841240204</v>
+        <v>1.298884610500811</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746930956054493</v>
+        <v>4.746046630148041</v>
       </c>
       <c r="K20" t="n">
-        <v>22.9006396483428</v>
+        <v>23.21183403563495</v>
       </c>
       <c r="L20" t="n">
-        <v>43.28367358368642</v>
+        <v>43.16516806295514</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95498603509179</v>
+        <v>99.95672824461482</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.79690370082244</v>
+        <v>82.49130527544447</v>
       </c>
       <c r="C21" t="n">
-        <v>37.19146136605147</v>
+        <v>37.02309591379419</v>
       </c>
       <c r="D21" t="n">
-        <v>1.182236640010936</v>
+        <v>1.183478589365685</v>
       </c>
       <c r="E21" t="n">
-        <v>13.63485477290051</v>
+        <v>13.48374849624742</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7601361937330706</v>
+        <v>0.7599704486787369</v>
       </c>
       <c r="G21" t="n">
-        <v>21.64494834224816</v>
+        <v>21.62529715986114</v>
       </c>
       <c r="H21" t="n">
-        <v>38.77254088691238</v>
+        <v>38.72388914090865</v>
       </c>
       <c r="I21" t="n">
-        <v>2.051335654185677</v>
+        <v>1.96510613614073</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750851210831692</v>
+        <v>4.749815304242104</v>
       </c>
       <c r="K21" t="n">
-        <v>17.20309629917756</v>
+        <v>17.50869472455551</v>
       </c>
       <c r="L21" t="n">
-        <v>45.53712090291253</v>
+        <v>45.40275779663904</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93167856814156</v>
+        <v>99.93454843498874</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_57_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.44395466523776</v>
+        <v>43.25237162247731</v>
       </c>
       <c r="M2" t="n">
-        <v>99.05742527850543</v>
+        <v>95.40644399724962</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05563682984919</v>
+        <v>81.48766028361847</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9367283594781</v>
+        <v>43.24321583917403</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228797162345612</v>
+        <v>2.180751381166168</v>
       </c>
       <c r="E3" t="n">
-        <v>5.712507988546333</v>
+        <v>4.151910738191487</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429323874485374</v>
+        <v>0.7376405713652199</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97561655126201</v>
+        <v>32.80213535837445</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17488982263271</v>
+        <v>33.93146628280011</v>
       </c>
       <c r="I3" t="n">
-        <v>6.577565496060616</v>
+        <v>3.073502380688416</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643327421553359</v>
+        <v>4.610253571032624</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94436317015081</v>
+        <v>18.51233971638152</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8828146487462</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639061783751</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09691673479496</v>
+        <v>88.53910586829542</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61468475789</v>
+        <v>42.79646366713447</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182398503910339</v>
+        <v>2.186487766989632</v>
       </c>
       <c r="E4" t="n">
-        <v>6.509057347639309</v>
+        <v>6.505475028876886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444941722852284</v>
+        <v>0.739580907596546</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26831888679857</v>
+        <v>33.47749447793964</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2467319251205</v>
+        <v>34.02072174944111</v>
       </c>
       <c r="I4" t="n">
-        <v>5.492827322258331</v>
+        <v>6.986965264973208</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653088576782677</v>
+        <v>4.622380672478412</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90308326520506</v>
+        <v>11.46089413170458</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29952182423659</v>
+        <v>45.51035438350518</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81728984733164</v>
+        <v>99.76771218234424</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.9559032470048</v>
+        <v>87.42477631251079</v>
       </c>
       <c r="C5" t="n">
-        <v>42.32614810649031</v>
+        <v>42.76512046797546</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126827759781893</v>
+        <v>2.133445976907209</v>
       </c>
       <c r="E5" t="n">
-        <v>7.107565519777093</v>
+        <v>7.320230297559509</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458180584142844</v>
+        <v>0.7412264248764463</v>
       </c>
       <c r="G5" t="n">
-        <v>32.42120263688852</v>
+        <v>32.66536725665215</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30763068705708</v>
+        <v>34.09641554431652</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585495719996656</v>
+        <v>5.835425656721156</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661362865089277</v>
+        <v>4.632665155477789</v>
       </c>
       <c r="K5" t="n">
-        <v>14.04409675299519</v>
+        <v>12.57522368748921</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47717660378513</v>
+        <v>44.46557347606387</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84742146327062</v>
+        <v>99.80591763152854</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.57569745851038</v>
+        <v>86.07640405514493</v>
       </c>
       <c r="C6" t="n">
-        <v>41.65808259192244</v>
+        <v>42.32237348428517</v>
       </c>
       <c r="D6" t="n">
-        <v>2.059459637173455</v>
+        <v>2.069043523379146</v>
       </c>
       <c r="E6" t="n">
-        <v>7.520265544622715</v>
+        <v>7.911259010701293</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469429888287863</v>
+        <v>0.7426249022121918</v>
       </c>
       <c r="G6" t="n">
-        <v>31.39424803545952</v>
+        <v>31.67929598065325</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35937748612417</v>
+        <v>34.16074550176081</v>
       </c>
       <c r="I6" t="n">
-        <v>3.827010086121819</v>
+        <v>4.872029497612028</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668393680179914</v>
+        <v>4.641405638826198</v>
       </c>
       <c r="K6" t="n">
-        <v>15.42430254148963</v>
+        <v>13.92359594485508</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7902399854769</v>
+        <v>43.59193541372861</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87262511888896</v>
+        <v>99.83790484286885</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.02398743488614</v>
+        <v>84.52010446148843</v>
       </c>
       <c r="C7" t="n">
-        <v>40.70073536108826</v>
+        <v>41.52259458684663</v>
       </c>
       <c r="D7" t="n">
-        <v>1.984006979552205</v>
+        <v>1.994943489997612</v>
       </c>
       <c r="E7" t="n">
-        <v>7.77695535157662</v>
+        <v>8.305683814967928</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479006180959755</v>
+        <v>0.7438159051805657</v>
       </c>
       <c r="G7" t="n">
-        <v>30.24405338947597</v>
+        <v>30.54474425994508</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40342843241487</v>
+        <v>34.21553163830601</v>
       </c>
       <c r="I7" t="n">
-        <v>3.193263800670644</v>
+        <v>4.066535945712699</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674378863099847</v>
+        <v>4.648849407378535</v>
       </c>
       <c r="K7" t="n">
-        <v>16.97601256511388</v>
+        <v>15.47989553851156</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21694623807227</v>
+        <v>42.86217572193037</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89369416427439</v>
+        <v>99.86466584728856</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.93808690409263</v>
+        <v>82.72500181388457</v>
       </c>
       <c r="C8" t="n">
-        <v>43.00963300447293</v>
+        <v>40.35888148161408</v>
       </c>
       <c r="D8" t="n">
-        <v>1.988274164126698</v>
+        <v>1.909876133232056</v>
       </c>
       <c r="E8" t="n">
-        <v>9.616622978580279</v>
+        <v>8.517086039249866</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495091960968018</v>
+        <v>0.7448329596574421</v>
       </c>
       <c r="G8" t="n">
-        <v>30.7477314019946</v>
+        <v>29.2422709466401</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47742302045287</v>
+        <v>34.26231614424233</v>
       </c>
       <c r="I8" t="n">
-        <v>5.674093667236359</v>
+        <v>3.393413593003773</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684432475605011</v>
+        <v>4.655205997859012</v>
       </c>
       <c r="K8" t="n">
-        <v>12.06191309590737</v>
+        <v>17.27499818611544</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73972336400342</v>
+        <v>42.25316100044513</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81126946438373</v>
+        <v>99.88704066817463</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.89995442376498</v>
+        <v>80.74169659051609</v>
       </c>
       <c r="C9" t="n">
-        <v>41.85207382536466</v>
+        <v>38.90206829888375</v>
       </c>
       <c r="D9" t="n">
-        <v>1.896071601313419</v>
+        <v>1.816510534132641</v>
       </c>
       <c r="E9" t="n">
-        <v>9.960186961496126</v>
+        <v>8.572580783674614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508869626276579</v>
+        <v>0.7457035275002682</v>
       </c>
       <c r="G9" t="n">
-        <v>29.3218618277131</v>
+        <v>27.81274256076506</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54080028087225</v>
+        <v>34.30236226501233</v>
       </c>
       <c r="I9" t="n">
-        <v>4.737103273319573</v>
+        <v>2.831149872554504</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693043516422861</v>
+        <v>4.660647046876676</v>
       </c>
       <c r="K9" t="n">
-        <v>14.10004557623502</v>
+        <v>19.2583034094839</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89026688542151</v>
+        <v>41.74536680293782</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8423862870212</v>
+        <v>99.90573851130547</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.73496801572254</v>
+        <v>85.5398576991028</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42195195529117</v>
+        <v>42.23090049199408</v>
       </c>
       <c r="D10" t="n">
-        <v>1.799210874209183</v>
+        <v>1.81852776691663</v>
       </c>
       <c r="E10" t="n">
-        <v>10.11033783689777</v>
+        <v>10.46308502793973</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520688091203176</v>
+        <v>0.7465316303791368</v>
       </c>
       <c r="G10" t="n">
-        <v>27.82395591808665</v>
+        <v>29.24965343144165</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5951652195346</v>
+        <v>35.74647985063885</v>
       </c>
       <c r="I10" t="n">
-        <v>3.953799300872056</v>
+        <v>2.84975730191719</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700430057001984</v>
+        <v>4.665822689869604</v>
       </c>
       <c r="K10" t="n">
-        <v>16.26503198427742</v>
+        <v>14.46014230089719</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18142985839476</v>
+        <v>43.21407066843297</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86841379796336</v>
+        <v>99.90511346132425</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.43544948115459</v>
+        <v>85.17243862078844</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73519369553374</v>
+        <v>42.22644603653634</v>
       </c>
       <c r="D11" t="n">
-        <v>1.697373332491654</v>
+        <v>1.798323299766804</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08796070466795</v>
+        <v>10.77436909339848</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530844549855022</v>
+        <v>0.7472424572093036</v>
       </c>
       <c r="G11" t="n">
-        <v>26.24908589469361</v>
+        <v>28.94671804353244</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6418849293331</v>
+        <v>35.80255495572248</v>
       </c>
       <c r="I11" t="n">
-        <v>3.299282321323405</v>
+        <v>2.43296541360077</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706777843659388</v>
+        <v>4.670265357558147</v>
       </c>
       <c r="K11" t="n">
-        <v>18.56455051884539</v>
+        <v>14.82756137921155</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5904280272633</v>
+        <v>42.8649708837608</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89017224164243</v>
+        <v>99.91897829950871</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.06569013593801</v>
+        <v>83.21207498747137</v>
       </c>
       <c r="C12" t="n">
-        <v>36.8759786973615</v>
+        <v>40.64420112359007</v>
       </c>
       <c r="D12" t="n">
-        <v>1.593464398384799</v>
+        <v>1.714807111998741</v>
       </c>
       <c r="E12" t="n">
-        <v>9.929166497008318</v>
+        <v>10.61218161616241</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539583842615295</v>
+        <v>0.7478498386073669</v>
       </c>
       <c r="G12" t="n">
-        <v>24.642182755363</v>
+        <v>27.60239939976782</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68208567603035</v>
+        <v>35.83165636139536</v>
       </c>
       <c r="I12" t="n">
-        <v>2.752592523255477</v>
+        <v>2.029119168243629</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712239901634559</v>
+        <v>4.674061491296042</v>
       </c>
       <c r="K12" t="n">
-        <v>20.93430986406197</v>
+        <v>16.78792501252862</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09806470742866</v>
+        <v>42.50029149128127</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90835326885214</v>
+        <v>99.93241762739996</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.72757760647109</v>
+        <v>84.39819311131123</v>
       </c>
       <c r="C13" t="n">
-        <v>34.96296402266951</v>
+        <v>41.63500536674938</v>
       </c>
       <c r="D13" t="n">
-        <v>1.491931144928959</v>
+        <v>1.716076029631949</v>
       </c>
       <c r="E13" t="n">
-        <v>9.679180200062151</v>
+        <v>11.25540422937678</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547104716633075</v>
+        <v>0.7484032302049178</v>
       </c>
       <c r="G13" t="n">
-        <v>23.07201840783095</v>
+        <v>27.94593081931053</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71668169651213</v>
+        <v>36.18127724090925</v>
       </c>
       <c r="I13" t="n">
-        <v>2.296115237577923</v>
+        <v>1.873581373097073</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716940447895672</v>
+        <v>4.677520188780735</v>
       </c>
       <c r="K13" t="n">
-        <v>23.27242239352892</v>
+        <v>15.60180688868876</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6881526803778</v>
+        <v>42.70078121151751</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92353909657622</v>
+        <v>99.93759346695565</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.58616995017464</v>
+        <v>82.49161943470986</v>
       </c>
       <c r="C14" t="n">
-        <v>39.09047789222888</v>
+        <v>40.01946026707516</v>
       </c>
       <c r="D14" t="n">
-        <v>1.49382224769342</v>
+        <v>1.637147214004103</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00523661948882</v>
+        <v>10.99810960546948</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556671076744141</v>
+        <v>0.7488756955574176</v>
       </c>
       <c r="G14" t="n">
-        <v>24.8853011952041</v>
+        <v>26.66059195139396</v>
       </c>
       <c r="H14" t="n">
-        <v>36.54472471930988</v>
+        <v>36.20411840355474</v>
       </c>
       <c r="I14" t="n">
-        <v>3.178498637838909</v>
+        <v>1.562303467496303</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722919422965088</v>
+        <v>4.680473097233859</v>
       </c>
       <c r="K14" t="n">
-        <v>16.41383004982538</v>
+        <v>17.50838056529015</v>
       </c>
       <c r="L14" t="n">
-        <v>44.38987623058905</v>
+        <v>42.42011524060421</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89418417264331</v>
+        <v>99.94795607296952</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.86649979557649</v>
+        <v>81.6571927909623</v>
       </c>
       <c r="C15" t="n">
-        <v>38.86181515960693</v>
+        <v>39.39976684535829</v>
       </c>
       <c r="D15" t="n">
-        <v>1.467377949487424</v>
+        <v>1.601920672866172</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23464364809204</v>
+        <v>10.98300804245828</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564731057899393</v>
+        <v>0.7492820521945769</v>
       </c>
       <c r="G15" t="n">
-        <v>24.44477065231781</v>
+        <v>26.0869352691458</v>
       </c>
       <c r="H15" t="n">
-        <v>36.58370349575391</v>
+        <v>36.22376356481856</v>
       </c>
       <c r="I15" t="n">
-        <v>2.651574032948237</v>
+        <v>1.329270363262814</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72795691118712</v>
+        <v>4.683012826216105</v>
       </c>
       <c r="K15" t="n">
-        <v>17.13350020442351</v>
+        <v>18.34280720903768</v>
       </c>
       <c r="L15" t="n">
-        <v>43.91639300714073</v>
+        <v>42.21314096351321</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91170837117116</v>
+        <v>99.9557150179092</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.54020934045552</v>
+        <v>79.41126820291097</v>
       </c>
       <c r="C16" t="n">
-        <v>36.94524907180904</v>
+        <v>37.35984233239999</v>
       </c>
       <c r="D16" t="n">
-        <v>1.37915468235703</v>
+        <v>1.509588726009328</v>
       </c>
       <c r="E16" t="n">
-        <v>11.86767058194127</v>
+        <v>10.53467315448498</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571655413187424</v>
+        <v>0.7496306109546619</v>
       </c>
       <c r="G16" t="n">
-        <v>22.97507599597247</v>
+        <v>24.58332927808315</v>
       </c>
       <c r="H16" t="n">
-        <v>36.61719028580866</v>
+        <v>36.24061450910153</v>
       </c>
       <c r="I16" t="n">
-        <v>2.211667619815196</v>
+        <v>1.108240605810684</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732284633242139</v>
+        <v>4.685191318466636</v>
       </c>
       <c r="K16" t="n">
-        <v>19.45979065954449</v>
+        <v>20.58873179708903</v>
       </c>
       <c r="L16" t="n">
-        <v>43.5213054343979</v>
+        <v>42.01450169375368</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92634516575143</v>
+        <v>99.96307582324269</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.27313148312975</v>
+        <v>84.16209260591694</v>
       </c>
       <c r="C17" t="n">
-        <v>38.19141587945891</v>
+        <v>40.50788520018743</v>
       </c>
       <c r="D17" t="n">
-        <v>1.380406326367006</v>
+        <v>1.510321067597868</v>
       </c>
       <c r="E17" t="n">
-        <v>12.67183197291431</v>
+        <v>12.20794807014588</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578527026114349</v>
+        <v>0.7499942766756534</v>
       </c>
       <c r="G17" t="n">
-        <v>23.41598528044157</v>
+        <v>26.05927323684526</v>
       </c>
       <c r="H17" t="n">
-        <v>37.07048039372905</v>
+        <v>37.72221372656892</v>
       </c>
       <c r="I17" t="n">
-        <v>2.239995415744902</v>
+        <v>1.224877998860514</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736579391321468</v>
+        <v>4.687464229222833</v>
       </c>
       <c r="K17" t="n">
-        <v>17.72686851687028</v>
+        <v>15.83790739408307</v>
       </c>
       <c r="L17" t="n">
-        <v>44.00711679154151</v>
+        <v>43.61339793685814</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92540118787068</v>
+        <v>99.95919053112864</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.03743670615663</v>
+        <v>85.87841339491234</v>
       </c>
       <c r="C18" t="n">
-        <v>36.30149197977025</v>
+        <v>41.23997882263066</v>
       </c>
       <c r="D18" t="n">
-        <v>1.299048634574488</v>
+        <v>1.511586532059265</v>
       </c>
       <c r="E18" t="n">
-        <v>12.2363384554295</v>
+        <v>12.81346226954927</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758442325071312</v>
+        <v>0.7506226802143087</v>
       </c>
       <c r="G18" t="n">
-        <v>22.03590575090325</v>
+        <v>26.19886140266157</v>
       </c>
       <c r="H18" t="n">
-        <v>37.09932186617252</v>
+        <v>37.75382033121763</v>
       </c>
       <c r="I18" t="n">
-        <v>1.868115142309856</v>
+        <v>2.158668427870866</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7402645316957</v>
+        <v>4.691391751339428</v>
       </c>
       <c r="K18" t="n">
-        <v>19.96256329384337</v>
+        <v>14.12158660508767</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6737226315046</v>
+        <v>44.56653919755618</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93777790511822</v>
+        <v>99.92810462527451</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.20691741827198</v>
+        <v>83.38690461864365</v>
       </c>
       <c r="C19" t="n">
-        <v>35.75867631452584</v>
+        <v>39.08283916764223</v>
       </c>
       <c r="D19" t="n">
-        <v>1.269550160517641</v>
+        <v>1.419671384569566</v>
       </c>
       <c r="E19" t="n">
-        <v>12.21810925033617</v>
+        <v>12.33434398700988</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589395412009224</v>
+        <v>0.7511628368050483</v>
       </c>
       <c r="G19" t="n">
-        <v>21.53551987095114</v>
+        <v>24.60578541341783</v>
       </c>
       <c r="H19" t="n">
-        <v>37.12364326889452</v>
+        <v>37.78098840835551</v>
       </c>
       <c r="I19" t="n">
-        <v>1.557783193865831</v>
+        <v>1.800184858454249</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743372132505765</v>
+        <v>4.69476773003155</v>
       </c>
       <c r="K19" t="n">
-        <v>20.793082581728</v>
+        <v>16.61309538135636</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39634901645977</v>
+        <v>44.24410243911612</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94810791271361</v>
+        <v>99.94003698811471</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.78816596436505</v>
+        <v>80.8427152605651</v>
       </c>
       <c r="C20" t="n">
-        <v>33.57972614602473</v>
+        <v>36.81679993850908</v>
       </c>
       <c r="D20" t="n">
-        <v>1.182539574937768</v>
+        <v>1.326332985280493</v>
       </c>
       <c r="E20" t="n">
-        <v>11.59720298702108</v>
+        <v>11.77358468421185</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593674608236867</v>
+        <v>0.7516277549761404</v>
       </c>
       <c r="G20" t="n">
-        <v>20.05954967850563</v>
+        <v>22.98804158290795</v>
       </c>
       <c r="H20" t="n">
-        <v>37.14457502242804</v>
+        <v>37.80437224362028</v>
       </c>
       <c r="I20" t="n">
-        <v>1.298884610500811</v>
+        <v>1.501082540967495</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746046630148041</v>
+        <v>4.697673468600876</v>
       </c>
       <c r="K20" t="n">
-        <v>23.21183403563495</v>
+        <v>19.15728473943492</v>
       </c>
       <c r="L20" t="n">
-        <v>43.16516806295514</v>
+        <v>43.97591018709894</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95672824461482</v>
+        <v>99.94999486504292</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.49130527544447</v>
+        <v>78.36228059840029</v>
       </c>
       <c r="C21" t="n">
-        <v>37.02309591379419</v>
+        <v>34.56763603145715</v>
       </c>
       <c r="D21" t="n">
-        <v>1.183478589365685</v>
+        <v>1.235827691522161</v>
       </c>
       <c r="E21" t="n">
-        <v>13.48374849624742</v>
+        <v>11.17878251563511</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599704486787369</v>
+        <v>0.752027910637185</v>
       </c>
       <c r="G21" t="n">
-        <v>21.62529715986114</v>
+        <v>21.41940121922896</v>
       </c>
       <c r="H21" t="n">
-        <v>38.72388914090865</v>
+        <v>37.82449874036732</v>
       </c>
       <c r="I21" t="n">
-        <v>1.96510613614073</v>
+        <v>1.251568079527141</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749815304242104</v>
+        <v>4.700174441482405</v>
       </c>
       <c r="K21" t="n">
-        <v>17.50869472455551</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="L21" t="n">
-        <v>45.40275779663904</v>
+        <v>43.75294782969407</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93454843498874</v>
+        <v>99.95830326275092</v>
       </c>
     </row>
   </sheetData>
